--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486526_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486526_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.7148</v>
+        <v>6.5953</v>
       </c>
       <c r="E2" t="n">
-        <v>3.8307</v>
+        <v>3.4954</v>
       </c>
       <c r="F2" t="n">
-        <v>2.8841</v>
+        <v>3.0999</v>
       </c>
       <c r="G2" t="n">
         <v>4.9782</v>
@@ -610,13 +610,13 @@
         <v>1.305</v>
       </c>
       <c r="S2" t="n">
-        <v>0.4539</v>
+        <v>0.3344</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5552</v>
+        <v>0.2199</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1013</v>
+        <v>0.1144</v>
       </c>
       <c r="V2" t="n">
         <v>0.1952</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. GODSPOWER JOHNSON</t>
+          <t>S. CECCARDI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.2057</v>
+        <v>2.7841</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1331</v>
+        <v>2.7731</v>
       </c>
       <c r="F3" t="n">
-        <v>3.0726</v>
+        <v>0.011</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.7171999999999999</v>
+        <v>3.6156</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4104</v>
+        <v>-0.803</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.1275</v>
+        <v>4.4186</v>
       </c>
       <c r="J3" t="n">
-        <v>-1.8685</v>
+        <v>3.6477</v>
       </c>
       <c r="K3" t="n">
-        <v>0.3467</v>
+        <v>-0.4681</v>
       </c>
       <c r="L3" t="n">
-        <v>-2.2152</v>
+        <v>4.1158</v>
       </c>
       <c r="M3" t="n">
-        <v>1.1513</v>
+        <v>-0.0321</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0636</v>
+        <v>-0.3348</v>
       </c>
       <c r="O3" t="n">
-        <v>1.0877</v>
+        <v>0.3028</v>
       </c>
       <c r="P3" t="n">
-        <v>1.0875</v>
+        <v>0.435</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-1.305</v>
       </c>
       <c r="R3" t="n">
-        <v>1.0875</v>
+        <v>1.7401</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5754</v>
+        <v>0.2539</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2584</v>
+        <v>-0.1346</v>
       </c>
       <c r="U3" t="n">
-        <v>0.8337</v>
+        <v>0.3884</v>
       </c>
       <c r="V3" t="n">
-        <v>2.2599</v>
+        <v>-1.5204</v>
       </c>
       <c r="W3" t="n">
-        <v>2.2599</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-2.0854</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. STILMA</t>
+          <t>J. GODSPOWER JOHNSON</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.0247</v>
+        <v>2.724</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7611</v>
+        <v>0.0213</v>
       </c>
       <c r="F4" t="n">
-        <v>1.2636</v>
+        <v>2.7027</v>
       </c>
       <c r="G4" t="n">
-        <v>1.2388</v>
+        <v>-0.7171999999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>1.6636</v>
+        <v>0.4104</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4247</v>
+        <v>-1.1275</v>
       </c>
       <c r="J4" t="n">
-        <v>1.5266</v>
+        <v>-1.8685</v>
       </c>
       <c r="K4" t="n">
-        <v>2.0804</v>
+        <v>0.3467</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.5538</v>
+        <v>-2.2152</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.2878</v>
+        <v>1.1513</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.4169</v>
+        <v>0.0636</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1291</v>
+        <v>1.0877</v>
       </c>
       <c r="P4" t="n">
         <v>1.0875</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.2175</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.305</v>
+        <v>1.0875</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.6714</v>
+        <v>0.09370000000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.548</v>
+        <v>-0.3701</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1234</v>
+        <v>0.4638</v>
       </c>
       <c r="V4" t="n">
-        <v>0.3698</v>
+        <v>2.2599</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>2.2599</v>
       </c>
       <c r="X4" t="n">
-        <v>0.3698</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. CECCARDI</t>
+          <t>M. STILMA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9872</v>
+        <v>2.4525</v>
       </c>
       <c r="E5" t="n">
-        <v>1.6987</v>
+        <v>1.0964</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2884</v>
+        <v>1.3561</v>
       </c>
       <c r="G5" t="n">
-        <v>3.6156</v>
+        <v>1.2388</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.803</v>
+        <v>1.6636</v>
       </c>
       <c r="I5" t="n">
-        <v>4.4186</v>
+        <v>-0.4247</v>
       </c>
       <c r="J5" t="n">
-        <v>3.6477</v>
+        <v>1.5266</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.4681</v>
+        <v>2.0804</v>
       </c>
       <c r="L5" t="n">
-        <v>4.1158</v>
+        <v>-0.5538</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.0321</v>
+        <v>-0.2878</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.3348</v>
+        <v>-0.4169</v>
       </c>
       <c r="O5" t="n">
-        <v>0.3028</v>
+        <v>0.1291</v>
       </c>
       <c r="P5" t="n">
-        <v>0.435</v>
+        <v>1.0875</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.305</v>
+        <v>-0.2175</v>
       </c>
       <c r="R5" t="n">
-        <v>1.7401</v>
+        <v>1.305</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.5431</v>
+        <v>-0.2436</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.2089</v>
+        <v>-0.2127</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6657999999999999</v>
+        <v>-0.031</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.5204</v>
+        <v>0.3698</v>
       </c>
       <c r="W5" t="n">
-        <v>0.5649999999999999</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.0854</v>
+        <v>0.3698</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.7808</v>
+        <v>1.2366</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.3755</v>
+        <v>-0.6423</v>
       </c>
       <c r="F6" t="n">
-        <v>2.1563</v>
+        <v>1.8789</v>
       </c>
       <c r="G6" t="n">
         <v>1.5788</v>
@@ -922,13 +922,13 @@
         <v>1.7401</v>
       </c>
       <c r="S6" t="n">
-        <v>0.8545</v>
+        <v>0.3103</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4062</v>
+        <v>0.1394</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4483</v>
+        <v>0.1709</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3775</v>
+        <v>-0.2622</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3178</v>
+        <v>-0.3528</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0598</v>
+        <v>0.0906</v>
       </c>
       <c r="G7" t="n">
         <v>-1.3251</v>
@@ -1000,13 +1000,13 @@
         <v>0.87</v>
       </c>
       <c r="S7" t="n">
-        <v>1.0071</v>
+        <v>0.3674</v>
       </c>
       <c r="T7" t="n">
-        <v>0.8977000000000001</v>
+        <v>0.2271</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1095</v>
+        <v>0.1403</v>
       </c>
       <c r="V7" t="n">
         <v>-0.1745</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. RODRIGUEZ FEBLES</t>
+          <t>N. HOOVER</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.9817</v>
+        <v>-0.5366</v>
       </c>
       <c r="E8" t="n">
-        <v>1.2175</v>
+        <v>-1.5474</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.1992</v>
+        <v>1.0109</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.3524</v>
+        <v>-0.8934</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1339</v>
+        <v>-0.8607</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.2185</v>
+        <v>-0.0326</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0663</v>
+        <v>-0.5857</v>
       </c>
       <c r="K8" t="n">
-        <v>0.7149</v>
+        <v>-0.7419</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6486</v>
+        <v>0.1562</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.4187</v>
+        <v>-0.3077</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.8488</v>
+        <v>-0.1188</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.5698</v>
+        <v>-0.1889</v>
       </c>
       <c r="P8" t="n">
-        <v>1.305</v>
+        <v>-1.9576</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-3.4801</v>
       </c>
       <c r="R8" t="n">
-        <v>1.305</v>
+        <v>1.5225</v>
       </c>
       <c r="S8" t="n">
-        <v>1.3909</v>
+        <v>0.2497</v>
       </c>
       <c r="T8" t="n">
-        <v>1.1512</v>
+        <v>0.2584</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2396</v>
+        <v>-0.008699999999999999</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.3252</v>
+        <v>2.0647</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2.2599</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.3252</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.2515</v>
+        <v>-0.9663</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.9906</v>
+        <v>-2.7671</v>
       </c>
       <c r="F9" t="n">
-        <v>1.7391</v>
+        <v>1.8008</v>
       </c>
       <c r="G9" t="n">
         <v>3.1109</v>
@@ -1156,13 +1156,13 @@
         <v>1.0875</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7725</v>
+        <v>-0.4873</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.0154</v>
+        <v>-0.7919</v>
       </c>
       <c r="U9" t="n">
-        <v>0.243</v>
+        <v>0.3046</v>
       </c>
       <c r="V9" t="n">
         <v>0.7602</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>N. HOOVER</t>
+          <t>J. GARCIA SANCHEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.7196</v>
+        <v>-1.3275</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.3298</v>
+        <v>-0.9154</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6102</v>
+        <v>-0.4122</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.8934</v>
+        <v>-0.4716</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.8607</v>
+        <v>-1.9649</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.0326</v>
+        <v>1.4933</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.5857</v>
+        <v>-0.21</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.7419</v>
+        <v>-1.3806</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1562</v>
+        <v>1.1706</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.3077</v>
+        <v>-0.2616</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1188</v>
+        <v>-0.5843</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.1889</v>
+        <v>0.3227</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.9576</v>
+        <v>0.87</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.4801</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5225</v>
+        <v>0.87</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.9334</v>
+        <v>-0.596</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5239</v>
+        <v>-0.7054</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4094</v>
+        <v>0.1093</v>
       </c>
       <c r="V10" t="n">
-        <v>2.0647</v>
+        <v>-1.13</v>
       </c>
       <c r="W10" t="n">
-        <v>2.2599</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.1952</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. GARCIA SANCHEZ</t>
+          <t>S. RODRIGUEZ FEBLES</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.9664</v>
+        <v>-2.0192</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.4309</v>
+        <v>0.0567</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.5355</v>
+        <v>-2.0759</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.4716</v>
+        <v>-2.3524</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.9649</v>
+        <v>-0.1339</v>
       </c>
       <c r="I11" t="n">
-        <v>1.4933</v>
+        <v>-2.2185</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.21</v>
+        <v>0.0663</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.3806</v>
+        <v>0.7149</v>
       </c>
       <c r="L11" t="n">
-        <v>1.1706</v>
+        <v>-0.6486</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.2616</v>
+        <v>-2.4187</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.5843</v>
+        <v>-0.8488</v>
       </c>
       <c r="O11" t="n">
-        <v>0.3227</v>
+        <v>-1.5698</v>
       </c>
       <c r="P11" t="n">
-        <v>0.87</v>
+        <v>1.305</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.87</v>
+        <v>1.305</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.2349</v>
+        <v>0.3533</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.2209</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.014</v>
+        <v>0.3629</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.13</v>
+        <v>-1.3252</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.13</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.5469</v>
+        <v>-3.7134</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.3764</v>
+        <v>-0.4196</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.1705</v>
+        <v>-3.2938</v>
       </c>
       <c r="G12" t="n">
         <v>-2.1052</v>
@@ -1390,13 +1390,13 @@
         <v>0.2175</v>
       </c>
       <c r="S12" t="n">
-        <v>0.5583</v>
+        <v>0.3918</v>
       </c>
       <c r="T12" t="n">
-        <v>0.5516</v>
+        <v>0.5083</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0067</v>
+        <v>-0.1166</v>
       </c>
       <c r="V12" t="n">
         <v>-1.13</v>
@@ -1423,19 +1423,19 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.624600000000002</v>
+        <v>6.967300000000002</v>
       </c>
       <c r="E13" t="n">
-        <v>0.4557000000000003</v>
+        <v>0.7982999999999991</v>
       </c>
       <c r="F13" t="n">
-        <v>6.168899999999999</v>
+        <v>6.169000000000001</v>
       </c>
       <c r="G13" t="n">
         <v>6.657400000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>2.310700000000001</v>
+        <v>2.310699999999999</v>
       </c>
       <c r="I13" t="n">
         <v>4.347</v>
@@ -1444,7 +1444,7 @@
         <v>9.1813</v>
       </c>
       <c r="K13" t="n">
-        <v>5.826200000000001</v>
+        <v>5.8262</v>
       </c>
       <c r="L13" t="n">
         <v>3.355100000000001</v>
@@ -1456,10 +1456,10 @@
         <v>-3.5156</v>
       </c>
       <c r="O13" t="n">
-        <v>0.9919999999999999</v>
+        <v>0.9919999999999992</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.087700000000001</v>
+        <v>-1.0877</v>
       </c>
       <c r="Q13" t="n">
         <v>-14.1379</v>
@@ -1468,22 +1468,22 @@
         <v>13.0502</v>
       </c>
       <c r="S13" t="n">
-        <v>0.6848000000000003</v>
+        <v>1.0276</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.2136</v>
+        <v>-0.8712000000000002</v>
       </c>
       <c r="U13" t="n">
-        <v>1.8985</v>
+        <v>1.8983</v>
       </c>
       <c r="V13" t="n">
-        <v>0.3697000000000004</v>
+        <v>0.3697000000000006</v>
       </c>
       <c r="W13" t="n">
-        <v>6.6259</v>
+        <v>6.625900000000001</v>
       </c>
       <c r="X13" t="n">
-        <v>-6.2561</v>
+        <v>-6.256099999999999</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.1957</v>
+        <v>2.9086</v>
       </c>
       <c r="E14" t="n">
-        <v>1.7654</v>
+        <v>1.8771</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4303</v>
+        <v>1.0314</v>
       </c>
       <c r="G14" t="n">
         <v>1.7677</v>
@@ -1546,13 +1546,13 @@
         <v>1.5225</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.7673</v>
+        <v>-0.0544</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.3629</v>
+        <v>-0.2511</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.4044</v>
+        <v>0.1968</v>
       </c>
       <c r="V14" t="n">
         <v>0.7602</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.9108</v>
+        <v>1.6256</v>
       </c>
       <c r="E15" t="n">
-        <v>1.4632</v>
+        <v>1.2397</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4476</v>
+        <v>0.3859</v>
       </c>
       <c r="G15" t="n">
         <v>1.7909</v>
@@ -1624,13 +1624,13 @@
         <v>0.87</v>
       </c>
       <c r="S15" t="n">
-        <v>0.5548999999999999</v>
+        <v>0.2698</v>
       </c>
       <c r="T15" t="n">
-        <v>0.4386</v>
+        <v>0.2151</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1163</v>
+        <v>0.0547</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.2128</v>
+        <v>0.9391</v>
       </c>
       <c r="E16" t="n">
-        <v>0.2095</v>
+        <v>-0.1258</v>
       </c>
       <c r="F16" t="n">
-        <v>1.0033</v>
+        <v>1.0649</v>
       </c>
       <c r="G16" t="n">
         <v>0.1406</v>
@@ -1702,13 +1702,13 @@
         <v>1.0875</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.0154</v>
+        <v>-0.289</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2776</v>
+        <v>-0.0577</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.293</v>
+        <v>-0.2313</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7513</v>
+        <v>0.9003</v>
       </c>
       <c r="E17" t="n">
         <v>0.1145</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6367</v>
+        <v>0.7857</v>
       </c>
       <c r="G17" t="n">
         <v>-0.7828000000000001</v>
@@ -1780,13 +1780,13 @@
         <v>1.0875</v>
       </c>
       <c r="S17" t="n">
-        <v>0.447</v>
+        <v>0.596</v>
       </c>
       <c r="T17" t="n">
         <v>-0.1334</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5804</v>
+        <v>0.7294</v>
       </c>
       <c r="V17" t="n">
         <v>1.3045</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>O. LO</t>
+          <t>S. THRASTARSON</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3145</v>
+        <v>0.8207</v>
       </c>
       <c r="E18" t="n">
-        <v>0.268</v>
+        <v>1.7328</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0465</v>
+        <v>-0.9121</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.4276</v>
+        <v>1.46</v>
       </c>
       <c r="H18" t="n">
-        <v>1.5088</v>
+        <v>-0.3983</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.9364</v>
+        <v>1.8583</v>
       </c>
       <c r="J18" t="n">
-        <v>1.0451</v>
+        <v>3.3686</v>
       </c>
       <c r="K18" t="n">
-        <v>1.5607</v>
+        <v>0.1341</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.5155999999999999</v>
+        <v>3.2345</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.4727</v>
+        <v>-1.9086</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.0519</v>
+        <v>-0.5324</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.4208</v>
+        <v>-1.3762</v>
       </c>
       <c r="P18" t="n">
-        <v>0.87</v>
+        <v>-1.305</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.435</v>
+        <v>-2.3926</v>
       </c>
       <c r="R18" t="n">
-        <v>1.305</v>
+        <v>1.0875</v>
       </c>
       <c r="S18" t="n">
-        <v>1.567</v>
+        <v>-0.4642</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0277</v>
+        <v>-0.5684</v>
       </c>
       <c r="U18" t="n">
-        <v>1.5394</v>
+        <v>0.1042</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.695</v>
+        <v>1.13</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.3698</v>
+        <v>1.3252</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.3252</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S. THRASTARSON</t>
+          <t>O. LO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1939</v>
+        <v>-0.1902</v>
       </c>
       <c r="E19" t="n">
-        <v>1.2858</v>
+        <v>0.3798</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.0919</v>
+        <v>-0.57</v>
       </c>
       <c r="G19" t="n">
-        <v>1.46</v>
+        <v>-0.4276</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.3983</v>
+        <v>1.5088</v>
       </c>
       <c r="I19" t="n">
-        <v>1.8583</v>
+        <v>-1.9364</v>
       </c>
       <c r="J19" t="n">
-        <v>3.3686</v>
+        <v>1.0451</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1341</v>
+        <v>1.5607</v>
       </c>
       <c r="L19" t="n">
-        <v>3.2345</v>
+        <v>-0.5155999999999999</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.9086</v>
+        <v>-1.4727</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.5324</v>
+        <v>-0.0519</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.3762</v>
+        <v>-1.4208</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.305</v>
+        <v>0.87</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.3926</v>
+        <v>-0.435</v>
       </c>
       <c r="R19" t="n">
-        <v>1.0875</v>
+        <v>1.305</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.091</v>
+        <v>1.0623</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.0154</v>
+        <v>0.1394</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0756</v>
+        <v>0.9229000000000001</v>
       </c>
       <c r="V19" t="n">
-        <v>1.13</v>
+        <v>-1.695</v>
       </c>
       <c r="W19" t="n">
-        <v>1.3252</v>
+        <v>-0.3698</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.1952</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1299</v>
+        <v>-0.3429</v>
       </c>
       <c r="E20" t="n">
-        <v>2.538</v>
+        <v>1.644</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.4082</v>
+        <v>-1.9869</v>
       </c>
       <c r="G20" t="n">
         <v>-1.2674</v>
@@ -2014,13 +2014,13 @@
         <v>0.6525</v>
       </c>
       <c r="S20" t="n">
-        <v>0.7023</v>
+        <v>0.2295</v>
       </c>
       <c r="T20" t="n">
-        <v>1.2161</v>
+        <v>0.3221</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5138</v>
+        <v>-0.0925</v>
       </c>
       <c r="V20" t="n">
         <v>1.13</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.8972</v>
+        <v>-1.2454</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.1176</v>
+        <v>-1.6764</v>
       </c>
       <c r="F21" t="n">
-        <v>0.2204</v>
+        <v>0.431</v>
       </c>
       <c r="G21" t="n">
         <v>-2.4284</v>
@@ -2092,13 +2092,13 @@
         <v>1.0875</v>
       </c>
       <c r="S21" t="n">
-        <v>0.6612</v>
+        <v>0.313</v>
       </c>
       <c r="T21" t="n">
-        <v>0.3377</v>
+        <v>-0.2211</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3235</v>
+        <v>0.5341</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.4304</v>
+        <v>-1.3643</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.3631</v>
+        <v>-3.6926</v>
       </c>
       <c r="F22" t="n">
-        <v>1.9327</v>
+        <v>2.3283</v>
       </c>
       <c r="G22" t="n">
         <v>-0.4285</v>
@@ -2170,13 +2170,13 @@
         <v>1.5225</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.7621</v>
+        <v>0.304</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7859</v>
+        <v>-0.1153</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0238</v>
+        <v>0.4194</v>
       </c>
       <c r="V22" t="n">
         <v>-0.3698</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.566</v>
+        <v>-2.0367</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.2428</v>
+        <v>-3.7958</v>
       </c>
       <c r="F23" t="n">
-        <v>1.6768</v>
+        <v>1.7591</v>
       </c>
       <c r="G23" t="n">
         <v>-3.3931</v>
@@ -2248,13 +2248,13 @@
         <v>1.0875</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2604</v>
+        <v>0.2689</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.7413999999999999</v>
+        <v>-0.2944</v>
       </c>
       <c r="U23" t="n">
-        <v>0.481</v>
+        <v>0.5633</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.4005</v>
+        <v>-2.9355</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.1161</v>
+        <v>-0.8925</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.2845</v>
+        <v>-2.043</v>
       </c>
       <c r="G24" t="n">
         <v>1.3133</v>
@@ -2326,13 +2326,13 @@
         <v>1.0875</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.1064</v>
+        <v>-0.6414</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.0719</v>
+        <v>-0.8484</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0345</v>
+        <v>0.207</v>
       </c>
       <c r="V24" t="n">
         <v>-3.3899</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.0392</v>
+        <v>-3.4689</v>
       </c>
       <c r="E25" t="n">
         <v>-2.9738</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.0655</v>
+        <v>-0.4951</v>
       </c>
       <c r="G25" t="n">
         <v>-4.4022</v>
@@ -2404,13 +2404,13 @@
         <v>1.7401</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.6148</v>
+        <v>-0.0445</v>
       </c>
       <c r="T25" t="n">
         <v>-0.0853</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.5295</v>
+        <v>0.0408</v>
       </c>
       <c r="V25" t="n">
         <v>0.7602</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-6.6244</v>
+        <v>-4.389600000000001</v>
       </c>
       <c r="E26" t="n">
         <v>-6.169</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.4557999999999998</v>
+        <v>1.779199999999999</v>
       </c>
       <c r="G26" t="n">
         <v>-6.6575</v>
@@ -2482,13 +2482,13 @@
         <v>14.1376</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.6850000000000001</v>
+        <v>1.55</v>
       </c>
       <c r="T26" t="n">
         <v>-1.8985</v>
       </c>
       <c r="U26" t="n">
-        <v>1.2136</v>
+        <v>3.4488</v>
       </c>
       <c r="V26" t="n">
         <v>-0.3698000000000004</v>
